--- a/astro-site/public/dl/coffee-shop-checklist-templates/09-cash-drawer-opening-closing.xlsx
+++ b/astro-site/public/dl/coffee-shop-checklist-templates/09-cash-drawer-opening-closing.xlsx
@@ -1203,7 +1203,7 @@
       </c>
       <c r="C5" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D5" s="32" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D6" s="32" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C7" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D7" s="32" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C8" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D8" s="32" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C9" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D9" s="32" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C10" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D10" s="32" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="C11" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D11" s="32" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="C12" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D12" s="32" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C13" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D13" s="32" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C14" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D14" s="32" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D15" s="32" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C5" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D5" s="32" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D6" s="32" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C7" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D7" s="32" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="C8" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D8" s="32" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C9" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D9" s="32" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C10" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D10" s="32" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="C11" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D11" s="32" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="C12" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D12" s="32" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="C13" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D13" s="32" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="C14" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D14" s="32" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D15" s="32" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="C16" s="32" t="inlineStr">
         <is>
-          <t>Cashier / MOD</t>
+          <t>Cashier / shift lead</t>
         </is>
       </c>
       <c r="D16" s="32" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>General manager: _________________________</t>
+          <t>Manager: _________________________</t>
         </is>
       </c>
     </row>
